--- a/file_IX_Tuesday_student_data.xlsx
+++ b/file_IX_Tuesday_student_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\29abh\Projects\RAC_Projects\RACOperationalApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{734C9BAB-B6BB-4E59-A62B-D82870F5F74B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D41DB7C-A708-477B-897F-040BAA3880CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="690" windowWidth="38380" windowHeight="20140" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="19380" windowHeight="20970" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Result" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
   <si>
     <t>Name</t>
   </si>
@@ -37,27 +37,6 @@
     <t>Remarks</t>
   </si>
   <si>
-    <t>Rannver</t>
-  </si>
-  <si>
-    <t>4, 5, 9 (diagram), 18, 20 (diagram)</t>
-  </si>
-  <si>
-    <t>Abhishek</t>
-  </si>
-  <si>
-    <t>adlk;lk;la;sd;l;a</t>
-  </si>
-  <si>
-    <t>s</t>
-  </si>
-  <si>
-    <t>d</t>
-  </si>
-  <si>
-    <t>f</t>
-  </si>
-  <si>
     <t xml:space="preserve">Name </t>
   </si>
   <si>
@@ -65,19 +44,157 @@
   </si>
   <si>
     <t>Roll Number</t>
+  </si>
+  <si>
+    <t>Aaditya</t>
+  </si>
+  <si>
+    <t>Aaren</t>
+  </si>
+  <si>
+    <t>Adrik</t>
+  </si>
+  <si>
+    <t>Aishani Jindal</t>
+  </si>
+  <si>
+    <t>Aradhya Kaushik</t>
+  </si>
+  <si>
+    <t>Aradhya Goswami</t>
+  </si>
+  <si>
+    <t>Arhant</t>
+  </si>
+  <si>
+    <t>Armaan Arora</t>
+  </si>
+  <si>
+    <t>Arth</t>
+  </si>
+  <si>
+    <t>Atharva raj</t>
+  </si>
+  <si>
+    <t>Bhavik</t>
+  </si>
+  <si>
+    <t>Rakshan Sharma</t>
+  </si>
+  <si>
+    <t>Kavyashree</t>
+  </si>
+  <si>
+    <t>Rushil</t>
+  </si>
+  <si>
+    <t>Jaishna Sharma</t>
+  </si>
+  <si>
+    <t>Jayesh Sharma</t>
+  </si>
+  <si>
+    <t>Kavya Tiwari</t>
+  </si>
+  <si>
+    <t>Kimaya Arora</t>
+  </si>
+  <si>
+    <t>Kritika</t>
+  </si>
+  <si>
+    <t>Lakshay</t>
+  </si>
+  <si>
+    <t>Lavanya</t>
+  </si>
+  <si>
+    <t>Avantika</t>
+  </si>
+  <si>
+    <t>Mahira Kathuria</t>
+  </si>
+  <si>
+    <t>Navish Sethi</t>
+  </si>
+  <si>
+    <t>Neev Virmani</t>
+  </si>
+  <si>
+    <t>Priyanshi</t>
+  </si>
+  <si>
+    <t>Raghav Sharma</t>
+  </si>
+  <si>
+    <t>Ranak</t>
+  </si>
+  <si>
+    <t>Riddhi Narwat</t>
+  </si>
+  <si>
+    <t>Rishita Sharma</t>
+  </si>
+  <si>
+    <t>Rushvi Goel</t>
+  </si>
+  <si>
+    <t>Saksham Singh</t>
+  </si>
+  <si>
+    <t>Samyak</t>
+  </si>
+  <si>
+    <t>Sasvika</t>
+  </si>
+  <si>
+    <t>Mihir</t>
+  </si>
+  <si>
+    <t>Mishika Sethi</t>
+  </si>
+  <si>
+    <t>Shresth</t>
+  </si>
+  <si>
+    <t>Shreya</t>
+  </si>
+  <si>
+    <t>Shruti</t>
+  </si>
+  <si>
+    <t>Sritha Reddy</t>
+  </si>
+  <si>
+    <t>Sumeera</t>
+  </si>
+  <si>
+    <t>Tanush</t>
+  </si>
+  <si>
+    <t>Vijaybala</t>
+  </si>
+  <si>
+    <t>Vrisha</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -88,7 +205,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -96,13 +213,34 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -383,7 +521,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="21.36328125" customWidth="1"/>
@@ -401,61 +539,6 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2">
-        <v>33</v>
-      </c>
-      <c r="C2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3">
-        <v>40</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4">
-        <v>39</v>
-      </c>
-      <c r="C4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5">
-        <v>39.5</v>
-      </c>
-      <c r="C5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6">
-        <v>33</v>
-      </c>
-      <c r="C6" t="s">
-        <v>4</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -463,63 +546,375 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FC8ABDE-9CD1-46A8-811F-2734DD2C7292}">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C45"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="31.453125" customWidth="1"/>
-    <col min="2" max="2" width="26.26953125" customWidth="1"/>
+    <col min="2" max="2" width="26.26953125" style="1" customWidth="1"/>
     <col min="3" max="3" width="28.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="3">
+        <v>919717597792</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="3">
+        <v>919910688288</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="3">
+        <v>919213998196</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="3">
+        <v>919711052627</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B6" s="3">
+        <v>918076461063</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C1" t="s">
+      <c r="B7" s="3">
+        <v>919015753604</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2">
-        <v>9811658385</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3">
-        <v>9811658385</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4">
-        <v>9811658385</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5">
-        <v>9811658385</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="1">
-        <v>919811658385</v>
+      <c r="B8" s="3">
+        <v>918826301252</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="3">
+        <v>919810498957</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="3">
+        <v>919166175098</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="3">
+        <v>919717478188</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="3">
+        <v>918178222358</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="3">
+        <v>919990523628</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="3">
+        <v>917838093099</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="3">
+        <v>919873915984</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" s="3">
+        <v>918979266934</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B17" s="3">
+        <v>919013771777</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" s="3">
+        <v>919211430317</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" s="3">
+        <v>919540310025</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B20" s="3">
+        <v>919210468731</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21" s="3">
+        <v>919873818205</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22" s="3">
+        <v>919213512676</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B23" s="3">
+        <v>919911182706</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B24" s="3">
+        <v>919654118833</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B25" s="3">
+        <v>919999571115</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B26" s="3">
+        <v>919999773379</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B27" s="3">
+        <v>919250906021</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B28" s="3">
+        <v>918130058088</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B29" s="3">
+        <v>918619193964</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B30" s="3">
+        <v>919953309007</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B31" s="3">
+        <v>919818308895</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B32" s="3">
+        <v>919999733552</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B33" s="3">
+        <v>918882022042</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B34" s="3">
+        <v>919650511886</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B35" s="3">
+        <v>919760355113</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A36" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B36" s="3">
+        <v>919891914449</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B37" s="3">
+        <v>918750272600</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A38" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B38" s="3">
+        <v>919355161777</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A39" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B39" s="3">
+        <v>917042007756</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A40" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B40" s="3">
+        <v>918851461662</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A41" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B41" s="3">
+        <v>919866225116</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A42" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B42" s="3">
+        <v>919999834111</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A43" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B43" s="3">
+        <v>919812165357</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A44" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B44" s="3">
+        <v>919999486145</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A45" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B45" s="3">
+        <v>919811348694</v>
       </c>
     </row>
   </sheetData>

--- a/file_IX_Tuesday_student_data.xlsx
+++ b/file_IX_Tuesday_student_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\29abh\Projects\RAC_Projects\RACOperationalApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D41DB7C-A708-477B-897F-040BAA3880CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05C6A959-D82E-493E-A251-6F18CB75DD75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="19380" windowHeight="20970" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1900" yWindow="1900" windowWidth="28800" windowHeight="15370" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Result" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>Name</t>
   </si>
@@ -44,138 +44,6 @@
   </si>
   <si>
     <t>Roll Number</t>
-  </si>
-  <si>
-    <t>Aaditya</t>
-  </si>
-  <si>
-    <t>Aaren</t>
-  </si>
-  <si>
-    <t>Adrik</t>
-  </si>
-  <si>
-    <t>Aishani Jindal</t>
-  </si>
-  <si>
-    <t>Aradhya Kaushik</t>
-  </si>
-  <si>
-    <t>Aradhya Goswami</t>
-  </si>
-  <si>
-    <t>Arhant</t>
-  </si>
-  <si>
-    <t>Armaan Arora</t>
-  </si>
-  <si>
-    <t>Arth</t>
-  </si>
-  <si>
-    <t>Atharva raj</t>
-  </si>
-  <si>
-    <t>Bhavik</t>
-  </si>
-  <si>
-    <t>Rakshan Sharma</t>
-  </si>
-  <si>
-    <t>Kavyashree</t>
-  </si>
-  <si>
-    <t>Rushil</t>
-  </si>
-  <si>
-    <t>Jaishna Sharma</t>
-  </si>
-  <si>
-    <t>Jayesh Sharma</t>
-  </si>
-  <si>
-    <t>Kavya Tiwari</t>
-  </si>
-  <si>
-    <t>Kimaya Arora</t>
-  </si>
-  <si>
-    <t>Kritika</t>
-  </si>
-  <si>
-    <t>Lakshay</t>
-  </si>
-  <si>
-    <t>Lavanya</t>
-  </si>
-  <si>
-    <t>Avantika</t>
-  </si>
-  <si>
-    <t>Mahira Kathuria</t>
-  </si>
-  <si>
-    <t>Navish Sethi</t>
-  </si>
-  <si>
-    <t>Neev Virmani</t>
-  </si>
-  <si>
-    <t>Priyanshi</t>
-  </si>
-  <si>
-    <t>Raghav Sharma</t>
-  </si>
-  <si>
-    <t>Ranak</t>
-  </si>
-  <si>
-    <t>Riddhi Narwat</t>
-  </si>
-  <si>
-    <t>Rishita Sharma</t>
-  </si>
-  <si>
-    <t>Rushvi Goel</t>
-  </si>
-  <si>
-    <t>Saksham Singh</t>
-  </si>
-  <si>
-    <t>Samyak</t>
-  </si>
-  <si>
-    <t>Sasvika</t>
-  </si>
-  <si>
-    <t>Mihir</t>
-  </si>
-  <si>
-    <t>Mishika Sethi</t>
-  </si>
-  <si>
-    <t>Shresth</t>
-  </si>
-  <si>
-    <t>Shreya</t>
-  </si>
-  <si>
-    <t>Shruti</t>
-  </si>
-  <si>
-    <t>Sritha Reddy</t>
-  </si>
-  <si>
-    <t>Sumeera</t>
-  </si>
-  <si>
-    <t>Tanush</t>
-  </si>
-  <si>
-    <t>Vijaybala</t>
-  </si>
-  <si>
-    <t>Vrisha</t>
   </si>
 </sst>
 </file>
@@ -566,356 +434,180 @@
       </c>
     </row>
     <row r="2" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="3">
-        <v>919717597792</v>
-      </c>
+      <c r="A2" s="2"/>
+      <c r="B2" s="3"/>
     </row>
     <row r="3" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="3">
-        <v>919910688288</v>
-      </c>
+      <c r="A3" s="2"/>
+      <c r="B3" s="3"/>
     </row>
     <row r="4" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="3">
-        <v>919213998196</v>
-      </c>
+      <c r="A4" s="2"/>
+      <c r="B4" s="3"/>
     </row>
     <row r="5" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="3">
-        <v>919711052627</v>
-      </c>
+      <c r="A5" s="2"/>
+      <c r="B5" s="3"/>
     </row>
     <row r="6" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="3">
-        <v>918076461063</v>
-      </c>
+      <c r="A6" s="2"/>
+      <c r="B6" s="3"/>
     </row>
     <row r="7" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="3">
-        <v>919015753604</v>
-      </c>
+      <c r="A7" s="2"/>
+      <c r="B7" s="3"/>
     </row>
     <row r="8" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="3">
-        <v>918826301252</v>
-      </c>
+      <c r="A8" s="2"/>
+      <c r="B8" s="3"/>
     </row>
     <row r="9" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="3">
-        <v>919810498957</v>
-      </c>
+      <c r="A9" s="2"/>
+      <c r="B9" s="3"/>
     </row>
     <row r="10" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="3">
-        <v>919166175098</v>
-      </c>
+      <c r="A10" s="2"/>
+      <c r="B10" s="3"/>
     </row>
     <row r="11" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" s="3">
-        <v>919717478188</v>
-      </c>
+      <c r="A11" s="2"/>
+      <c r="B11" s="3"/>
     </row>
     <row r="12" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" s="3">
-        <v>918178222358</v>
-      </c>
+      <c r="A12" s="2"/>
+      <c r="B12" s="3"/>
     </row>
     <row r="13" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B13" s="3">
-        <v>919990523628</v>
-      </c>
+      <c r="A13" s="2"/>
+      <c r="B13" s="3"/>
     </row>
     <row r="14" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B14" s="3">
-        <v>917838093099</v>
-      </c>
+      <c r="A14" s="2"/>
+      <c r="B14" s="3"/>
     </row>
     <row r="15" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B15" s="3">
-        <v>919873915984</v>
-      </c>
+      <c r="A15" s="2"/>
+      <c r="B15" s="3"/>
     </row>
     <row r="16" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B16" s="3">
-        <v>918979266934</v>
-      </c>
+      <c r="A16" s="2"/>
+      <c r="B16" s="3"/>
     </row>
     <row r="17" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B17" s="3">
-        <v>919013771777</v>
-      </c>
+      <c r="A17" s="2"/>
+      <c r="B17" s="3"/>
     </row>
     <row r="18" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B18" s="3">
-        <v>919211430317</v>
-      </c>
+      <c r="A18" s="2"/>
+      <c r="B18" s="3"/>
     </row>
     <row r="19" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B19" s="3">
-        <v>919540310025</v>
-      </c>
+      <c r="A19" s="2"/>
+      <c r="B19" s="3"/>
     </row>
     <row r="20" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B20" s="3">
-        <v>919210468731</v>
-      </c>
+      <c r="A20" s="2"/>
+      <c r="B20" s="3"/>
     </row>
     <row r="21" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B21" s="3">
-        <v>919873818205</v>
-      </c>
+      <c r="A21" s="2"/>
+      <c r="B21" s="3"/>
     </row>
     <row r="22" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B22" s="3">
-        <v>919213512676</v>
-      </c>
+      <c r="A22" s="2"/>
+      <c r="B22" s="3"/>
     </row>
     <row r="23" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B23" s="3">
-        <v>919911182706</v>
-      </c>
+      <c r="A23" s="2"/>
+      <c r="B23" s="3"/>
     </row>
     <row r="24" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B24" s="3">
-        <v>919654118833</v>
-      </c>
+      <c r="A24" s="2"/>
+      <c r="B24" s="3"/>
     </row>
     <row r="25" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B25" s="3">
-        <v>919999571115</v>
-      </c>
+      <c r="A25" s="2"/>
+      <c r="B25" s="3"/>
     </row>
     <row r="26" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B26" s="3">
-        <v>919999773379</v>
-      </c>
+      <c r="A26" s="2"/>
+      <c r="B26" s="3"/>
     </row>
     <row r="27" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B27" s="3">
-        <v>919250906021</v>
-      </c>
+      <c r="A27" s="2"/>
+      <c r="B27" s="3"/>
     </row>
     <row r="28" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B28" s="3">
-        <v>918130058088</v>
-      </c>
+      <c r="A28" s="2"/>
+      <c r="B28" s="3"/>
     </row>
     <row r="29" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B29" s="3">
-        <v>918619193964</v>
-      </c>
+      <c r="A29" s="2"/>
+      <c r="B29" s="3"/>
     </row>
     <row r="30" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B30" s="3">
-        <v>919953309007</v>
-      </c>
+      <c r="A30" s="2"/>
+      <c r="B30" s="3"/>
     </row>
     <row r="31" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B31" s="3">
-        <v>919818308895</v>
-      </c>
+      <c r="A31" s="2"/>
+      <c r="B31" s="3"/>
     </row>
     <row r="32" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B32" s="3">
-        <v>919999733552</v>
-      </c>
+      <c r="A32" s="2"/>
+      <c r="B32" s="3"/>
     </row>
     <row r="33" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B33" s="3">
-        <v>918882022042</v>
-      </c>
+      <c r="A33" s="2"/>
+      <c r="B33" s="3"/>
     </row>
     <row r="34" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B34" s="3">
-        <v>919650511886</v>
-      </c>
+      <c r="A34" s="2"/>
+      <c r="B34" s="3"/>
     </row>
     <row r="35" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B35" s="3">
-        <v>919760355113</v>
-      </c>
+      <c r="A35" s="2"/>
+      <c r="B35" s="3"/>
     </row>
     <row r="36" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B36" s="3">
-        <v>919891914449</v>
-      </c>
+      <c r="A36" s="2"/>
+      <c r="B36" s="3"/>
     </row>
     <row r="37" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B37" s="3">
-        <v>918750272600</v>
-      </c>
+      <c r="A37" s="2"/>
+      <c r="B37" s="3"/>
     </row>
     <row r="38" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A38" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B38" s="3">
-        <v>919355161777</v>
-      </c>
+      <c r="A38" s="2"/>
+      <c r="B38" s="3"/>
     </row>
     <row r="39" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B39" s="3">
-        <v>917042007756</v>
-      </c>
+      <c r="A39" s="2"/>
+      <c r="B39" s="3"/>
     </row>
     <row r="40" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B40" s="3">
-        <v>918851461662</v>
-      </c>
+      <c r="A40" s="2"/>
+      <c r="B40" s="3"/>
     </row>
     <row r="41" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B41" s="3">
-        <v>919866225116</v>
-      </c>
+      <c r="A41" s="2"/>
+      <c r="B41" s="3"/>
     </row>
     <row r="42" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B42" s="3">
-        <v>919999834111</v>
-      </c>
+      <c r="A42" s="2"/>
+      <c r="B42" s="3"/>
     </row>
     <row r="43" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B43" s="3">
-        <v>919812165357</v>
-      </c>
+      <c r="A43" s="2"/>
+      <c r="B43" s="3"/>
     </row>
     <row r="44" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B44" s="3">
-        <v>919999486145</v>
-      </c>
+      <c r="A44" s="2"/>
+      <c r="B44" s="3"/>
     </row>
     <row r="45" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A45" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B45" s="3">
-        <v>919811348694</v>
-      </c>
+      <c r="A45" s="2"/>
+      <c r="B45" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/file_IX_Tuesday_student_data.xlsx
+++ b/file_IX_Tuesday_student_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\29abh\Projects\RAC_Projects\RACOperationalApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05C6A959-D82E-493E-A251-6F18CB75DD75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6438562-609A-4FD7-BB19-9B80D4FCA671}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1900" yWindow="1900" windowWidth="28800" windowHeight="15370" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22540" yWindow="10510" windowWidth="14240" windowHeight="10450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Result" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Name</t>
   </si>
@@ -44,6 +44,12 @@
   </si>
   <si>
     <t>Roll Number</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>2, 5, 6</t>
   </si>
 </sst>
 </file>
@@ -389,7 +395,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="21.36328125" customWidth="1"/>
@@ -405,6 +411,17 @@
       </c>
       <c r="C1" t="s">
         <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2">
+        <v>39</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
